--- a/03_Cluster_groups/Muscle_size/04_Set_Contrasts/c_data/set_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_size/04_Set_Contrasts/c_data/set_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9837" uniqueCount="2933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9834" uniqueCount="2931">
   <si>
     <t>sheet</t>
   </si>
@@ -8351,7 +8351,7 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>fit</t>
@@ -8814,12 +8814,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>writexl</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
   </si>
 </sst>
 </file>
@@ -65604,7 +65598,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -66388,17 +66382,6 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>2931</v>
-      </c>
-      <c r="B72" t="s">
-        <v>2932</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2899</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/03_Cluster_groups/Muscle_size/04_Set_Contrasts/c_data/set_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_size/04_Set_Contrasts/c_data/set_contrasts.xlsx
@@ -8348,7 +8348,7 @@
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>
@@ -8360,7 +8360,7 @@
     <t>03_Cluster_groups/Muscle_size/03_Protein_Contrasts/c_data/fit.rds</t>
   </si>
   <si>
-    <t>b3ff32ecf599cffb3031cdaf013ee5d6</t>
+    <t>34bec5d571c34586ff8965599ef68697</t>
   </si>
   <si>
     <t>design</t>
@@ -8369,19 +8369,19 @@
     <t>03_Cluster_groups/Muscle_size/02_Design_Contrasts/c_data/design.rds</t>
   </si>
   <si>
-    <t>71d8f66ddabfb881cce04715444ff1b1</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/inputs/DAList_limpa.rds</t>
-  </si>
-  <si>
-    <t>dd3dacf79d5a8a76fc860eec1e69e162</t>
+    <t>c4dd3f50a2d661a4b677d8502617baaf</t>
+  </si>
+  <si>
+    <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
+  </si>
+  <si>
+    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
   </si>
   <si>
     <t>singscore</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/inputs/singscore.rds</t>
+    <t>01_Processing/05_Set_Scores/c_data/singscore.rds</t>
   </si>
   <si>
     <t>4f1249d3e2d6782468d2836f84bdc76a</t>
